--- a/data/externalStats/File1/RPT_RPT2771077013843XC_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT2771077013843XC_externalStats.xlsx
@@ -2057,13 +2057,13 @@
         <v>11630</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>302767.3</v>
+        <v>302767.2999999999</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>340247</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>26.03330180567498</v>
+        <v>26.03330180567497</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>29.25597592433362</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>4892930.933363182</v>
+        <v>9981855.828124575</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>7094.223987863295</v>
+        <v>7094.223987863296</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>1137649.238541728</v>
+        <v>2422416.600282871</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>3839.768428087868</v>
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1018887.825845929</v>
+        <v>2142347.757133012</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>98.75586356316637</v>
@@ -2288,13 +2288,13 @@
         <v>13991</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>419837.6900000001</v>
+        <v>419837.6899999999</v>
       </c>
       <c r="F28" s="66" t="n">
         <v>534426</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>30.00769709098707</v>
+        <v>30.00769709098706</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>38.19784146951612</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>922989.096049894</v>
+        <v>1873593.242555784</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>206.6628976952519</v>
@@ -2371,7 +2371,7 @@
         <v>261463</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>81.18517123287674</v>
+        <v>81.18517123287673</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>47.12743330930065</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>741685.7279853394</v>
+        <v>1505562.063517899</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>633.4919905024962</v>
@@ -2442,13 +2442,13 @@
         <v>19539</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>870253.0200000003</v>
+        <v>870253.02</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>795889.0000000001</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>44.53928143712576</v>
+        <v>44.53928143712575</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.7333538052101</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>652032.8396146006</v>
+        <v>1386204.128622586</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1320.996003648514</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>613984.5859231483</v>
+        <v>1246339.069597023</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>73.85994933226121</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>556393.580935954</v>
+        <v>1129420.996611712</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>827.1029214485163</v>
@@ -2659,7 +2659,7 @@
         <v>5145932</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>55.23706857566056</v>
+        <v>55.23706857566055</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.12068941272423</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>416982.3548995709</v>
+        <v>886493.1745864323</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>744.9370369136477</v>
@@ -2736,7 +2736,7 @@
         <v>19553344</v>
       </c>
       <c r="G34" s="52" t="n">
-        <v>104.2267537280878</v>
+        <v>104.2267537280877</v>
       </c>
       <c r="H34" s="53" t="n">
         <v>87.04069513812843</v>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>402909.8891882321</v>
+        <v>818046.5254240141</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>49.94371127615922</v>
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>389920.0275498342</v>
+        <v>791952.3506112064</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>63.84706288580607</v>
@@ -2884,13 +2884,13 @@
         <v>441470</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35602246.06500001</v>
+        <v>35602246.065</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25008150</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.64476876118424</v>
+        <v>80.64476876118422</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.64745056289215</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>341666.6811537879</v>
+        <v>693555.7394511132</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>77.61799801803876</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>264989.019245023</v>
+        <v>537906.2850620301</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>87.51283463479388</v>
@@ -3044,7 +3044,7 @@
         <v>25048402</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.72709704800637</v>
+        <v>80.72709704800634</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.62204128134473</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>214780.9246557284</v>
+        <v>435987.9123025983</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>46.40696764769305</v>
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>198669.4007004459</v>
+        <v>422365.7563700509</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>199.9395963677785</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>164038.3631917798</v>
+        <v>348741.1101001308</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>424.6489436386092</v>
@@ -3251,7 +3251,7 @@
         <v>5486179</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>53.72736373577039</v>
+        <v>53.72736373577037</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.38616088295825</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>159246.7222244203</v>
+        <v>323257.9712325261</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>39.72744946561649</v>
@@ -3328,7 +3328,7 @@
         <v>19741600</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>103.6807104558114</v>
+        <v>103.6807104558113</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>86.9919272393979</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>139773.1853297166</v>
+        <v>297621.5101687518</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>26.03484726071667</v>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>122337.3954337064</v>
+        <v>260085.9839135935</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>358.4698264140781</v>
+        <v>358.4698264140782</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -3482,7 +3482,7 @@
         <v>25542576</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>79.08928262793083</v>
+        <v>79.08928262793081</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>56.08070943505591</v>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>119720.1244139953</v>
+        <v>254521.7367272214</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>45.33514103688</v>
@@ -3595,13 +3595,13 @@
         <v>461917.9999999999</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>36582225.48500001</v>
+        <v>36582225.485</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>25844291</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>79.19636274187197</v>
+        <v>79.19636274187194</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>55.94995432089678</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>5449324.514299135</v>
+        <v>11111276.82473629</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>7921.326909311812</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>2842858.074754622</v>
+        <v>5770944.075598664</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>669.0619305189701</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>1190518.938638467</v>
+        <v>2534992.985716474</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>4332.556564335096</v>
@@ -3877,7 +3877,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1018887.825845929</v>
+        <v>2142347.757133012</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>105.235297543295</v>
@@ -3935,10 +3935,10 @@
         <v>3190.244751579447</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>1582.361608270012</v>
+        <v>1582.361608270013</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1576.830955050484</v>
+        <v>1576.830955050485</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>18.90392960196367</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>3178.09649292246</v>
+        <v>3178.096492922461</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>896301.72929841</v>
+        <v>1905513.16154475</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>2061.115682405011</v>
@@ -3986,28 +3986,28 @@
         <v>3982</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>3542.055182527252</v>
+        <v>3542.055182527251</v>
       </c>
       <c r="K54" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>5098.787055046999</v>
+        <v>5098.787055046998</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>3687.309245058492</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>837300.0587997427</v>
+        <v>1700161.596902902</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>652.3122535299487</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>11128.94415726921</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>747781.7797073268</v>
+        <v>1517942.017911614</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>675.9605782379678</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>416982.3548995709</v>
+        <v>886493.1745864324</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>745.3347419242058</v>
@@ -4229,13 +4229,13 @@
         <v>4506</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>1993.796490046238</v>
+        <v>1993.796490046237</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1170.184652629847</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>15.11113882740952</v>
+        <v>15.11113882740953</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>61.09093980085366</v>
@@ -4244,7 +4244,7 @@
         <v>3240.183221304347</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>1868.70084065676</v>
+        <v>1868.700840656761</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1085.072807591809</v>
@@ -4253,10 +4253,10 @@
         <v>12.50626329688559</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>60.91742114734843</v>
+        <v>60.91742114734842</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>3027.197332692803</v>
+        <v>3027.197332692804</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1591.150856265248</v>
@@ -4278,14 +4278,14 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>322415.4981058275</v>
+        <v>676887.4930972724</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>599.495057839081</v>
+        <v>247.8555116827157</v>
       </c>
     </row>
     <row r="58">
@@ -4359,14 +4359,14 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>318389.5251144412</v>
+        <v>661756.9488406472</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>247.8555116827157</v>
+        <v>599.495057839081</v>
       </c>
     </row>
     <row r="59">
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>216387.1877603706</v>
+        <v>439468.4601539859</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>443.4901730916443</v>
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>BASAL INSULIN</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>179489.2160809928</v>
+        <v>361396.8328375593</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>1789.282579852615</v>
+        <v>506.7380949249888</v>
       </c>
     </row>
     <row r="61">
@@ -4602,14 +4602,14 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>BASAL INSULIN</t>
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>172675.0309476871</v>
+        <v>364344.4070045526</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>506.7380949249889</v>
+        <v>1789.282579852615</v>
       </c>
     </row>
     <row r="62">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>146461.4714313991</v>
+        <v>311862.9957965406</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>39.5343976921994</v>
@@ -4724,25 +4724,25 @@
         <v>35.33749470904132</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>4438.794081799459</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>2084.050763884925</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>36.15759299573634</v>
+        <v>36.15759299573628</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>427.0257108888128</v>
+        <v>427.0257108888129</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>4588.731260960696</v>
+        <v>4588.731260960689</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2089.05312889332</v>
@@ -4751,13 +4751,13 @@
         <v>2139.669162986289</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>37.02035917201493</v>
+        <v>37.02035917201496</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>4743.404806421916</v>
+        <v>4743.404806421915</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>137793.6486695603</v>
+        <v>292945.5589945677</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>516.191071043153</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>134883.7489481329</v>
+        <v>276520.1287128018</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>255.2446894575277</v>
@@ -4897,7 +4897,7 @@
         <v>36614.95080324461</v>
       </c>
       <c r="P65" s="133" t="n">
-        <v>17969.80795994496</v>
+        <v>17969.80795994497</v>
       </c>
       <c r="Q65" s="134" t="n">
         <v>9277.056971434564</v>
@@ -4906,10 +4906,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S65" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>27906.60196401714</v>
+        <v>27906.60196401715</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>15805.42420356766</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>110842.2821414018</v>
+        <v>236018.4274519872</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>97.19850129494911</v>
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>99531.42426042404</v>
+        <v>210576.4597146778</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>296.8783488091591</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>80578.73846609288</v>
+        <v>169996.9038963505</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>142.7523736965244</v>
@@ -5135,7 +5135,7 @@
         <v>289.1746794647207</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>996.7440921888074</v>
+        <v>996.7440921888075</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>63795.46038650115</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>74723.81623725274</v>
+        <v>155028.0816239202</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>269.6079750699695</v>
@@ -5336,7 +5336,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>9.13465504001347</v>
+        <v>9.134655040013469</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>5.086047772684145</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>14.22070281269762</v>
+        <v>14.22070281269761</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>9.637479088489158</v>
@@ -5369,7 +5369,7 @@
         <v>10.21236598571077</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>4.502300675384264</v>
+        <v>4.502300675384263</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -5403,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="P72" s="130" t="n">
         <v>0.9053496785836537</v>
@@ -5604,7 +5604,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8475.980194421152</v>
+        <v>8475.980194421149</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2873.388189285528</v>
@@ -5616,7 +5616,7 @@
         <v>21.5477444020895</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>11448.18834161465</v>
+        <v>11448.18834161464</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>9595.485484687017</v>
@@ -5634,7 +5634,7 @@
         <v>13104.65405550815</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>11757.0132811728</v>
+        <v>11757.01328117279</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3999.28898659296</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>4.547473508864641e-13</v>
@@ -6018,13 +6018,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -6033,13 +6033,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -6048,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.092726157978177e-12</v>
       </c>
     </row>
     <row r="82">
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="133" t="n">
-        <v>39.06922934125345</v>
+        <v>39.06922934125344</v>
       </c>
       <c r="K83" s="134" t="n">
         <v>1.904687071596461</v>
@@ -6157,10 +6157,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="135" t="n">
-        <v>40.97391641284991</v>
+        <v>40.9739164128499</v>
       </c>
       <c r="P83" s="133" t="n">
-        <v>46.73956313840376</v>
+        <v>46.73956313840377</v>
       </c>
       <c r="Q83" s="134" t="n">
         <v>2.252055773796713</v>
@@ -6172,7 +6172,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="135" t="n">
-        <v>48.99161891220047</v>
+        <v>48.99161891220048</v>
       </c>
       <c r="V83" s="133" t="n">
         <v>55.9718148645036</v>
@@ -6360,7 +6360,7 @@
         <v>11529.82467663058</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>9677.960572529688</v>
+        <v>9677.96057252969</v>
       </c>
       <c r="Q86" s="143" t="n">
         <v>3401.224593286631</v>
@@ -6583,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>3192.811159583555</v>
+        <v>3192.811159583556</v>
       </c>
     </row>
     <row r="90">
@@ -6608,28 +6608,28 @@
         <v>3983</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>3543.039089320718</v>
+        <v>3543.039089320716</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>5099.770961840464</v>
+        <v>5099.770961840463</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>3688.214594737075</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -6644,13 +6644,13 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>5522.659551408971</v>
+        <v>5522.65955140897</v>
       </c>
     </row>
     <row r="91">
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>11128.94415726921</v>
@@ -6827,7 +6827,7 @@
         <v>11464.18632534378</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>4479.265978155642</v>
+        <v>4479.265978155641</v>
       </c>
       <c r="R93" s="131" t="n">
         <v>104.6184252717065</v>
@@ -6836,10 +6836,10 @@
         <v>83.78065942982869</v>
       </c>
       <c r="T93" s="132" t="n">
-        <v>16131.85138820096</v>
+        <v>16131.85138820095</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>13348.16413743805</v>
+        <v>13348.16413743804</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>5019.402142181207</v>
@@ -6851,7 +6851,7 @@
         <v>85.27829498014675</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>18577.58299574259</v>
+        <v>18577.58299574258</v>
       </c>
     </row>
     <row r="94">
@@ -7211,7 +7211,7 @@
         <v>3191</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1996.206591488692</v>
+        <v>1996.206591488699</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>2030.397059103354</v>
@@ -7220,25 +7220,25 @@
         <v>35.33749470904138</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>4438.794081799455</v>
+        <v>4438.794081799462</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>2084.050763884923</v>
+        <v>2084.050763884927</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>36.15759299573637</v>
+        <v>36.15759299573631</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>427.0257108888129</v>
+        <v>427.025710888813</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>4588.731260960694</v>
+        <v>4588.731260960691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2089.05312889332</v>
@@ -7250,10 +7250,10 @@
         <v>37.02035917201493</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>4743.404806421918</v>
+        <v>4743.404806421917</v>
       </c>
     </row>
     <row r="100">
@@ -7374,10 +7374,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S101" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>27955.59358292934</v>
+        <v>27955.59358292935</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>15861.39601843217</v>
@@ -7589,7 +7589,7 @@
         <v>307.7863336322335</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>1075.40901075923</v>
+        <v>1075.409010759229</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>66399.31889208843</v>
@@ -8581,13 +8581,13 @@
         <v>11630</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>302767.3</v>
+        <v>302767.2999999999</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>340247</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>26.03330180567498</v>
+        <v>26.03330180567497</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>29.25597592433362</v>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>6251111.142429027</v>
+        <v>12933826.60598246</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>8867.763082677957</v>
+        <v>8867.763082677959</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>1375555.251815606</v>
+        <v>2987039.848824577</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>4530.926745143684</v>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1259042.30028364</v>
+        <v>2671377.630346464</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>106.5953217954573</v>
@@ -8812,13 +8812,13 @@
         <v>13991</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>419837.6900000001</v>
+        <v>419837.6899999999</v>
       </c>
       <c r="F28" s="66" t="n">
         <v>534426</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>30.00769709098707</v>
+        <v>30.00769709098706</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>38.19784146951612</v>
@@ -8856,10 +8856,10 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>956945.8094923764</v>
+        <v>1965690.667440383</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>786.2501824315785</v>
+        <v>786.2501824315787</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -8895,7 +8895,7 @@
         <v>261463</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>81.18517123287674</v>
+        <v>81.18517123287673</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>47.12743330930065</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>925990.6538354389</v>
+        <v>1902104.767402549</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>210.9337439138654</v>
@@ -8966,13 +8966,13 @@
         <v>19539</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>870253.0200000003</v>
+        <v>870253.02</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>795889.0000000001</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>44.53928143712576</v>
+        <v>44.53928143712575</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.7333538052101</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>756353.9740596517</v>
+        <v>1553649.050283393</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>86.67421890565328</v>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>707877.5699479786</v>
+        <v>1534087.629355631</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1381.867499496638</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>634763.5969597775</v>
+        <v>1303902.223635008</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>926.3552720223383</v>
@@ -9183,7 +9183,7 @@
         <v>5145932</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>55.23706857566056</v>
+        <v>55.23706857566055</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.12068941272423</v>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>531542.6162420154</v>
+        <v>1091402.0989657</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>60.51929213888594</v>
+        <v>60.51929213888593</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -9260,7 +9260,7 @@
         <v>19553344</v>
       </c>
       <c r="G34" s="52" t="n">
-        <v>104.2267537280878</v>
+        <v>104.2267537280877</v>
       </c>
       <c r="H34" s="53" t="n">
         <v>87.04069513812843</v>
@@ -9289,19 +9289,19 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>NUBEQA</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>443674.8284724187</v>
+        <v>938344.3040652488</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>67.42696770181324</v>
+        <v>747.2463417280802</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -9366,19 +9366,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>NUBEQA</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>432982.3623017127</v>
+        <v>910469.8850609957</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>747.2463417280802</v>
+        <v>67.42696770181324</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -9408,13 +9408,13 @@
         <v>441470</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35602246.06500001</v>
+        <v>35602246.065</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25008150</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.64476876118424</v>
+        <v>80.64476876118422</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.64745056289215</v>
@@ -9452,7 +9452,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>380626.4780169133</v>
+        <v>781856.0969669089</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>81.9700391669102</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>339856.1558529094</v>
+        <v>698108.5733439856</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>105.5377103166963</v>
@@ -9568,7 +9568,7 @@
         <v>25048402</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.72709704800637</v>
+        <v>80.72709704800634</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.62204128134473</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>226725.6982738865</v>
+        <v>465723.9571405776</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>47.27663422141082</v>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>213662.0559240661</v>
+        <v>463040.9703190468</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>206.1997051300536</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>178998.6780293986</v>
+        <v>387919.7043297928</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>444.2167669614764</v>
@@ -9775,7 +9775,7 @@
         <v>5486179</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>53.72736373577039</v>
+        <v>53.72736373577037</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.38616088295825</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>169562.3643292192</v>
+        <v>348303.0635641523</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>40.493010198489</v>
@@ -9852,7 +9852,7 @@
         <v>19741600</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>103.6807104558114</v>
+        <v>103.6807104558113</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>86.9919272393979</v>
@@ -9881,19 +9881,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>TYMLOS</t>
+          <t>VUMERITY</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>138488.7168553741</v>
+        <v>298874.2267202126</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>82.82883027932023</v>
+        <v>24.4810875761971</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9958,19 +9958,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>VUMERITY</t>
+          <t>TYMLOS</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>137633.9228815761</v>
+        <v>284245.105497011</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>24.4810875761971</v>
+        <v>82.82883027932023</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -10006,7 +10006,7 @@
         <v>25542576</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>79.08928262793083</v>
+        <v>79.08928262793081</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>56.08070943505591</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>130915.3156911004</v>
+        <v>283715.115185333</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>367.4459108674866</v>
@@ -10119,13 +10119,13 @@
         <v>461917.9999999999</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>36582225.48500001</v>
+        <v>36582225.485</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>25844291</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>79.19636274187197</v>
+        <v>79.19636274187194</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>55.94995432089678</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>6885874.739388803</v>
+        <v>14237728.82961747</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>9794.118354700295</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3229846.106860065</v>
+        <v>6634067.04071752</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>718.9678557596146</v>
@@ -10280,7 +10280,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>1441332.43069695</v>
+        <v>3129876.026580798</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>5112.416745915412</v>
@@ -10401,7 +10401,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1259042.30028364</v>
+        <v>2671377.630346464</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>113.7874935134</v>
@@ -10459,10 +10459,10 @@
         <v>3190.244751579447</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>1582.361608270012</v>
+        <v>1582.361608270013</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1576.830955050484</v>
+        <v>1576.830955050485</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>18.90392960196367</v>
@@ -10471,7 +10471,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>3178.09649292246</v>
+        <v>3178.096492922461</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>973668.2488543665</v>
+        <v>2110099.936876958</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>2156.091893050233</v>
+        <v>2156.091893050234</v>
       </c>
     </row>
     <row r="54">
@@ -10510,28 +10510,28 @@
         <v>3982</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>3542.055182527252</v>
+        <v>3542.055182527251</v>
       </c>
       <c r="K54" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>5098.787055046999</v>
+        <v>5098.787055046998</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>3687.309245058492</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -10546,7 +10546,7 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>963692.9791075393</v>
+        <v>1979539.671437035</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>829.9331289332138</v>
@@ -10618,7 +10618,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>11128.94415726921</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>943982.787409073</v>
+        <v>1938020.871778333</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>678.7772727688632</v>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>432982.3623017127</v>
+        <v>938344.3040652488</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>747.3720653707389</v>
+        <v>747.3720653707388</v>
       </c>
     </row>
     <row r="57">
@@ -10753,13 +10753,13 @@
         <v>4506</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>1993.796490046238</v>
+        <v>1993.796490046237</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1170.184652629847</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>15.11113882740952</v>
+        <v>15.11113882740953</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>61.09093980085366</v>
@@ -10768,7 +10768,7 @@
         <v>3240.183221304347</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>1868.70084065676</v>
+        <v>1868.700840656761</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1085.072807591809</v>
@@ -10777,10 +10777,10 @@
         <v>12.50626329688559</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>60.91742114734843</v>
+        <v>60.91742114734842</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>3027.197332692803</v>
+        <v>3027.197332692804</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1591.150856265248</v>
@@ -10806,7 +10806,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>366161.443470569</v>
+        <v>764026.6212383567</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>647.8862989078516</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>341753.0522418778</v>
+        <v>740635.3188692254</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>255.731305786959</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>246128.8706814447</v>
+        <v>505111.4249711782</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>453.4952827410561</v>
@@ -11049,7 +11049,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>179165.5444324094</v>
+        <v>368033.6315804806</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>1708.084936378903</v>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>162262.252991763</v>
+        <v>348348.9951766971</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>296.9210423521528</v>
@@ -11211,7 +11211,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>154211.7933059894</v>
+        <v>328814.3542735458</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>416.3022366870206</v>
@@ -11248,25 +11248,25 @@
         <v>35.33749470904132</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>4438.794081799459</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>2084.050763884925</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>36.15759299573634</v>
+        <v>36.15759299573628</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>427.0257108888128</v>
+        <v>427.0257108888129</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>4588.731260960696</v>
+        <v>4588.731260960689</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2089.05312889332</v>
@@ -11275,13 +11275,13 @@
         <v>2139.669162986289</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>37.02035917201493</v>
+        <v>37.02035917201496</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>4743.404806421916</v>
+        <v>4743.404806421915</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>144256.7982565916</v>
+        <v>313255.9046883342</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>37.17498483792894</v>
@@ -11373,10 +11373,10 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>141962.3975513979</v>
+        <v>307655.9664593841</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>514.7302503121008</v>
+        <v>514.7302503121009</v>
       </c>
     </row>
     <row r="65">
@@ -11421,7 +11421,7 @@
         <v>36614.95080324461</v>
       </c>
       <c r="P65" s="133" t="n">
-        <v>17969.80795994496</v>
+        <v>17969.80795994497</v>
       </c>
       <c r="Q65" s="134" t="n">
         <v>9277.056971434564</v>
@@ -11430,10 +11430,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S65" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>27906.60196401714</v>
+        <v>27906.60196401715</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>15805.42420356766</v>
@@ -11459,7 +11459,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>129100.8280808892</v>
+        <v>280344.4772464589</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>108.3578612286222</v>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>104415.5459886615</v>
+        <v>225433.8348825983</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>293.9451907229246</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>96929.9945144081</v>
+        <v>208530.0767260928</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>160.9632940089901</v>
@@ -11659,7 +11659,7 @@
         <v>289.1746794647207</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>996.7440921888074</v>
+        <v>996.7440921888075</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>63795.46038650115</v>
@@ -11703,7 +11703,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>84557.08086043796</v>
+        <v>175325.4132666948</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>217.7919818643116</v>
@@ -11860,7 +11860,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>9.13465504001347</v>
+        <v>9.134655040013469</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>5.086047772684145</v>
@@ -11872,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>14.22070281269762</v>
+        <v>14.22070281269761</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>9.637479088489158</v>
@@ -11893,7 +11893,7 @@
         <v>10.21236598571077</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>4.502300675384264</v>
+        <v>4.502300675384263</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -11927,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>0</v>
@@ -11939,7 +11939,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="P72" s="130" t="n">
         <v>0.9053496785836537</v>
@@ -12128,7 +12128,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8475.980194421152</v>
+        <v>8475.980194421149</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2873.388189285528</v>
@@ -12140,7 +12140,7 @@
         <v>21.5477444020895</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>11448.18834161465</v>
+        <v>11448.18834161464</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>9595.485484687017</v>
@@ -12158,7 +12158,7 @@
         <v>13104.65405550815</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>11757.0132811728</v>
+        <v>11757.01328117279</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3999.28898659296</v>
@@ -12530,7 +12530,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>4.547473508864641e-13</v>
@@ -12542,13 +12542,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -12557,13 +12557,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.092726157978177e-12</v>
       </c>
     </row>
     <row r="82">
@@ -12669,7 +12669,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="133" t="n">
-        <v>39.06922934125345</v>
+        <v>39.06922934125344</v>
       </c>
       <c r="K83" s="134" t="n">
         <v>1.904687071596461</v>
@@ -12681,10 +12681,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="135" t="n">
-        <v>40.97391641284991</v>
+        <v>40.9739164128499</v>
       </c>
       <c r="P83" s="133" t="n">
-        <v>46.73956313840376</v>
+        <v>46.73956313840377</v>
       </c>
       <c r="Q83" s="134" t="n">
         <v>2.252055773796713</v>
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="135" t="n">
-        <v>48.99161891220047</v>
+        <v>48.99161891220048</v>
       </c>
       <c r="V83" s="133" t="n">
         <v>55.9718148645036</v>
@@ -12884,7 +12884,7 @@
         <v>11529.82467663058</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>9677.960572529688</v>
+        <v>9677.96057252969</v>
       </c>
       <c r="Q86" s="143" t="n">
         <v>3401.224593286631</v>
@@ -13107,7 +13107,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>3192.811159583555</v>
+        <v>3192.811159583556</v>
       </c>
     </row>
     <row r="90">
@@ -13132,28 +13132,28 @@
         <v>3983</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>3543.039089320718</v>
+        <v>3543.039089320716</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>5099.770961840464</v>
+        <v>5099.770961840463</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>3688.214594737075</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -13168,13 +13168,13 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>5522.659551408971</v>
+        <v>5522.65955140897</v>
       </c>
     </row>
     <row r="91">
@@ -13226,7 +13226,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>11128.94415726921</v>
@@ -13351,7 +13351,7 @@
         <v>11464.18632534378</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>4479.265978155642</v>
+        <v>4479.265978155641</v>
       </c>
       <c r="R93" s="131" t="n">
         <v>104.6184252717065</v>
@@ -13360,10 +13360,10 @@
         <v>83.78065942982869</v>
       </c>
       <c r="T93" s="132" t="n">
-        <v>16131.85138820096</v>
+        <v>16131.85138820095</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>13348.16413743805</v>
+        <v>13348.16413743804</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>5019.402142181207</v>
@@ -13375,7 +13375,7 @@
         <v>85.27829498014675</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>18577.58299574259</v>
+        <v>18577.58299574258</v>
       </c>
     </row>
     <row r="94">
@@ -13735,7 +13735,7 @@
         <v>3191</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1996.206591488692</v>
+        <v>1996.206591488699</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>2030.397059103354</v>
@@ -13744,25 +13744,25 @@
         <v>35.33749470904138</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>4438.794081799455</v>
+        <v>4438.794081799462</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>2084.050763884923</v>
+        <v>2084.050763884927</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>36.15759299573637</v>
+        <v>36.15759299573631</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>427.0257108888129</v>
+        <v>427.025710888813</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>4588.731260960694</v>
+        <v>4588.731260960691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2089.05312889332</v>
@@ -13774,10 +13774,10 @@
         <v>37.02035917201493</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>4743.404806421918</v>
+        <v>4743.404806421917</v>
       </c>
     </row>
     <row r="100">
@@ -13898,10 +13898,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S101" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>27955.59358292934</v>
+        <v>27955.59358292935</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>15861.39601843217</v>
@@ -14113,7 +14113,7 @@
         <v>307.7863336322335</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>1075.40901075923</v>
+        <v>1075.409010759229</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>66399.31889208843</v>
@@ -15105,13 +15105,13 @@
         <v>11630</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>302767.3</v>
+        <v>302767.2999999999</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>340247</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>26.03330180567498</v>
+        <v>26.03330180567497</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>29.25597592433362</v>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7751805.56619507</v>
+        <v>16231543.32840474</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>10641.30259354557</v>
@@ -15226,10 +15226,10 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>1695643.9826171</v>
+        <v>3720660.570081986</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>5346.493559269546</v>
+        <v>5346.493559269547</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -15303,10 +15303,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1212027.850529313</v>
+        <v>2520427.259206363</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>946.1752814417065</v>
+        <v>946.1752814417064</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -15336,13 +15336,13 @@
         <v>13991</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>419837.6900000001</v>
+        <v>419837.6899999999</v>
       </c>
       <c r="F28" s="66" t="n">
         <v>534426</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>30.00769709098707</v>
+        <v>30.00769709098706</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>38.19784146951612</v>
@@ -15380,7 +15380,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>945879.1686444322</v>
+        <v>1966779.816770341</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>216.9379906999112</v>
@@ -15419,7 +15419,7 @@
         <v>261463</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>81.18517123287674</v>
+        <v>81.18517123287673</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>47.12743330930065</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>931682.8708103144</v>
+        <v>1937261.255649032</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>100.8279847010699</v>
@@ -15490,13 +15490,13 @@
         <v>19539</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>870253.0200000003</v>
+        <v>870253.02</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>795889.0000000001</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>44.53928143712576</v>
+        <v>44.53928143712575</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.7333538052101</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>777838.394519011</v>
+        <v>1702994.085385665</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1445.543953873443</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>728342.3037163918</v>
+        <v>1514655.446638134</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1028.254351944796</v>
@@ -15668,7 +15668,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>694989.2287344952</v>
+        <v>1443031.160920639</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>72.12326121359592</v>
@@ -15707,7 +15707,7 @@
         <v>5145932</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>55.23706857566056</v>
+        <v>55.23706857566055</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.12068941272423</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>506390.9374226347</v>
+        <v>1049812.731910949</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>71.61687947480391</v>
@@ -15784,7 +15784,7 @@
         <v>19553344</v>
       </c>
       <c r="G34" s="52" t="n">
-        <v>104.2267537280878</v>
+        <v>104.2267537280877</v>
       </c>
       <c r="H34" s="53" t="n">
         <v>87.04069513812843</v>
@@ -15822,7 +15822,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>453716.6716498772</v>
+        <v>993364.1919777023</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>747.6050199721097</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>432982.520598896</v>
+        <v>900306.6255795482</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>125.3390419709598</v>
@@ -15932,13 +15932,13 @@
         <v>441470</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35602246.06500001</v>
+        <v>35602246.065</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25008150</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.64476876118424</v>
+        <v>80.64476876118422</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.64745056289215</v>
@@ -15976,7 +15976,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>429364.8849806063</v>
+        <v>892784.4251184907</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>87.06365740074202</v>
@@ -16044,19 +16044,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>COSENTYX UNOREADY</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>242977.5944233093</v>
+        <v>509560.9163477951</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>48.53182885998928</v>
+        <v>212.4125022456222</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -16092,7 +16092,7 @@
         <v>25048402</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.72709704800637</v>
+        <v>80.72709704800634</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.62204128134473</v>
@@ -16121,19 +16121,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>232740.7056095824</v>
+        <v>505226.7186770205</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>212.4125022456222</v>
+        <v>48.53182885998928</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>197828.3449973315</v>
+        <v>433124.0317089492</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>464.6862755830611</v>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>183513.4338729395</v>
+        <v>381582.055945662</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>41.58948411261035</v>
@@ -16299,7 +16299,7 @@
         <v>5486179</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>53.72736373577039</v>
+        <v>53.72736373577037</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.38616088295825</v>
@@ -16328,19 +16328,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>TYMLOS</t>
+          <t>INGREZZA</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>MOVEMENT DISORDER DRUG THERAPY</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>155733.7821494394</v>
+        <v>339039.6626094644</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>85.34599843150879</v>
+        <v>121.7259705683973</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -16376,7 +16376,7 @@
         <v>19741600</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>103.6807104558114</v>
+        <v>103.6807104558113</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>86.9919272393979</v>
@@ -16405,19 +16405,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>INGREZZA</t>
+          <t>TYMLOS</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>MOVEMENT DISORDER DRUG THERAPY</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>154513.0368502286</v>
+        <v>322997.753715795</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>121.7259705683973</v>
+        <v>85.34599843150879</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>141906.624262088</v>
+        <v>310689.3970499103</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>376.6467564756085</v>
@@ -16530,7 +16530,7 @@
         <v>25542576</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>79.08928262793083</v>
+        <v>79.08928262793081</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>56.08070943505591</v>
@@ -16559,19 +16559,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>EMGALITY</t>
+          <t>VUMERITY</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>139062.0382789588</v>
+        <v>304859.1171270079</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>259.2755881015718</v>
+        <v>23.19656491107404</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -16643,13 +16643,13 @@
         <v>461917.9999999999</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>36582225.48500001</v>
+        <v>36582225.485</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>25844291</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>79.19636274187197</v>
+        <v>79.19636274187194</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>55.94995432089678</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>8480147.86991146</v>
+        <v>17746198.77504288</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>11669.55694549037</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>3701477.325182108</v>
+        <v>7694464.011405854</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>772.4932947302113</v>
@@ -16804,7 +16804,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>1779089.689511347</v>
+        <v>3903761.005413257</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>6032.651760180186</v>
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1219526.091664303</v>
+        <v>2535978.719331997</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>990.8952888338557</v>
@@ -16983,10 +16983,10 @@
         <v>3190.244751579447</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>1582.361608270012</v>
+        <v>1582.361608270013</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1576.830955050484</v>
+        <v>1576.830955050485</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>18.90392960196367</v>
@@ -16995,21 +16995,21 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>3178.09649292246</v>
+        <v>3178.096492922461</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1072685.604882355</v>
+        <v>2344365.381746232</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>706.7347613825715</v>
+        <v>2255.444607481988</v>
       </c>
     </row>
     <row r="54">
@@ -17034,28 +17034,28 @@
         <v>3982</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>3542.055182527252</v>
+        <v>3542.055182527251</v>
       </c>
       <c r="K54" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>5098.787055046999</v>
+        <v>5098.787055046998</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>3687.309245058492</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -17070,7 +17070,7 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -17083,14 +17083,14 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1070783.169684629</v>
+        <v>2226741.732696893</v>
       </c>
       <c r="AH54" s="56" t="n">
-        <v>2255.444607481988</v>
+        <v>706.7347613825715</v>
       </c>
     </row>
     <row r="55">
@@ -17142,7 +17142,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>11128.94415726921</v>
@@ -17168,7 +17168,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>453716.6716498772</v>
+        <v>993364.1919777022</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>747.6382961599423</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>419479.4145506945</v>
+        <v>885065.0694781177</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>698.3955147707077</v>
@@ -17277,13 +17277,13 @@
         <v>4506</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>1993.796490046238</v>
+        <v>1993.796490046237</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1170.184652629847</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>15.11113882740952</v>
+        <v>15.11113882740953</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>61.09093980085366</v>
@@ -17292,7 +17292,7 @@
         <v>3240.183221304347</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>1868.70084065676</v>
+        <v>1868.700840656761</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1085.072807591809</v>
@@ -17301,10 +17301,10 @@
         <v>12.50626329688559</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>60.91742114734843</v>
+        <v>60.91742114734842</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>3027.197332692803</v>
+        <v>3027.197332692804</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1591.150856265248</v>
@@ -17330,7 +17330,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>371355.5921359737</v>
+        <v>813043.405209535</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>263.5868932360615</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>274532.4673509641</v>
+        <v>569216.9767728213</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>466.7352780197294</v>
@@ -17492,7 +17492,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>191769.7954469988</v>
+        <v>415320.4745822054</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>333.5521913471379</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>179429.5985283569</v>
+        <v>373063.9803597819</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>1630.332910074935</v>
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>167713.2129229483</v>
+        <v>362101.3404857772</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>410.8441051456194</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>154513.0368502286</v>
+        <v>339039.6626094644</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>121.7259705683973</v>
@@ -17772,25 +17772,25 @@
         <v>35.33749470904132</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>4438.794081799459</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>2084.050763884925</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>36.15759299573634</v>
+        <v>36.15759299573628</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>427.0257108888128</v>
+        <v>427.0257108888129</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>4588.731260960696</v>
+        <v>4588.731260960689</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2089.05312889332</v>
@@ -17799,13 +17799,13 @@
         <v>2139.669162986289</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>37.02035917201493</v>
+        <v>37.02035917201496</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>4743.404806421916</v>
+        <v>4743.404806421915</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>147832.4418971785</v>
+        <v>323663.3418368265</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>512.2543978080996</v>
@@ -17897,10 +17897,10 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>145669.3224652003</v>
+        <v>319634.3748587563</v>
       </c>
       <c r="AH64" s="56" t="n">
-        <v>35.2244133834828</v>
+        <v>35.22441338348281</v>
       </c>
     </row>
     <row r="65">
@@ -17945,7 +17945,7 @@
         <v>36614.95080324461</v>
       </c>
       <c r="P65" s="133" t="n">
-        <v>17969.80795994496</v>
+        <v>17969.80795994497</v>
       </c>
       <c r="Q65" s="134" t="n">
         <v>9277.056971434564</v>
@@ -17954,10 +17954,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S65" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>27906.60196401714</v>
+        <v>27906.60196401715</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>15805.42420356766</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>117218.0483036788</v>
+        <v>254156.1013906776</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>181.1384332800769</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>110715.0804387968</v>
+        <v>241205.6428255418</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>291.0410122385821</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>63144.63416840845</v>
+        <v>138248.4321555471</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>214.4654026029866</v>
@@ -18183,7 +18183,7 @@
         <v>289.1746794647207</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>996.7440921888074</v>
+        <v>996.7440921888075</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>63795.46038650115</v>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>60872.08663939586</v>
+        <v>133272.9320671779</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>162.3561125682152</v>
@@ -18384,7 +18384,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>9.13465504001347</v>
+        <v>9.134655040013469</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>5.086047772684145</v>
@@ -18396,7 +18396,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>14.22070281269762</v>
+        <v>14.22070281269761</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>9.637479088489158</v>
@@ -18417,7 +18417,7 @@
         <v>10.21236598571077</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>4.502300675384264</v>
+        <v>4.502300675384263</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -18451,7 +18451,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>0</v>
@@ -18463,7 +18463,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="P72" s="130" t="n">
         <v>0.9053496785836537</v>
@@ -18652,7 +18652,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8475.980194421152</v>
+        <v>8475.980194421149</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2873.388189285528</v>
@@ -18664,7 +18664,7 @@
         <v>21.5477444020895</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>11448.18834161465</v>
+        <v>11448.18834161464</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>9595.485484687017</v>
@@ -18682,7 +18682,7 @@
         <v>13104.65405550815</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>11757.0132811728</v>
+        <v>11757.01328117279</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3999.28898659296</v>
@@ -19054,7 +19054,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>4.547473508864641e-13</v>
@@ -19066,13 +19066,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -19081,13 +19081,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -19096,7 +19096,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.092726157978177e-12</v>
       </c>
     </row>
     <row r="82">
@@ -19193,7 +19193,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="133" t="n">
-        <v>39.06922934125345</v>
+        <v>39.06922934125344</v>
       </c>
       <c r="K83" s="134" t="n">
         <v>1.904687071596461</v>
@@ -19205,10 +19205,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="135" t="n">
-        <v>40.97391641284991</v>
+        <v>40.9739164128499</v>
       </c>
       <c r="P83" s="133" t="n">
-        <v>46.73956313840376</v>
+        <v>46.73956313840377</v>
       </c>
       <c r="Q83" s="134" t="n">
         <v>2.252055773796713</v>
@@ -19220,7 +19220,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="135" t="n">
-        <v>48.99161891220047</v>
+        <v>48.99161891220048</v>
       </c>
       <c r="V83" s="133" t="n">
         <v>55.9718148645036</v>
@@ -19408,7 +19408,7 @@
         <v>11529.82467663058</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>9677.960572529688</v>
+        <v>9677.96057252969</v>
       </c>
       <c r="Q86" s="143" t="n">
         <v>3401.224593286631</v>
@@ -19631,7 +19631,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>3192.811159583555</v>
+        <v>3192.811159583556</v>
       </c>
     </row>
     <row r="90">
@@ -19656,28 +19656,28 @@
         <v>3983</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>3543.039089320718</v>
+        <v>3543.039089320716</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>5099.770961840464</v>
+        <v>5099.770961840463</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>3688.214594737075</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -19692,13 +19692,13 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>5522.659551408971</v>
+        <v>5522.65955140897</v>
       </c>
     </row>
     <row r="91">
@@ -19750,7 +19750,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>11128.94415726921</v>
@@ -19875,7 +19875,7 @@
         <v>11464.18632534378</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>4479.265978155642</v>
+        <v>4479.265978155641</v>
       </c>
       <c r="R93" s="131" t="n">
         <v>104.6184252717065</v>
@@ -19884,10 +19884,10 @@
         <v>83.78065942982869</v>
       </c>
       <c r="T93" s="132" t="n">
-        <v>16131.85138820096</v>
+        <v>16131.85138820095</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>13348.16413743805</v>
+        <v>13348.16413743804</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>5019.402142181207</v>
@@ -19899,7 +19899,7 @@
         <v>85.27829498014675</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>18577.58299574259</v>
+        <v>18577.58299574258</v>
       </c>
     </row>
     <row r="94">
@@ -20259,7 +20259,7 @@
         <v>3191</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1996.206591488692</v>
+        <v>1996.206591488699</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>2030.397059103354</v>
@@ -20268,25 +20268,25 @@
         <v>35.33749470904138</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>4438.794081799455</v>
+        <v>4438.794081799462</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>2084.050763884923</v>
+        <v>2084.050763884927</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>36.15759299573637</v>
+        <v>36.15759299573631</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>427.0257108888129</v>
+        <v>427.025710888813</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>4588.731260960694</v>
+        <v>4588.731260960691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2089.05312889332</v>
@@ -20298,10 +20298,10 @@
         <v>37.02035917201493</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>4743.404806421918</v>
+        <v>4743.404806421917</v>
       </c>
     </row>
     <row r="100">
@@ -20422,10 +20422,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S101" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>27955.59358292934</v>
+        <v>27955.59358292935</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>15861.39601843217</v>
@@ -20637,7 +20637,7 @@
         <v>307.7863336322335</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>1075.40901075923</v>
+        <v>1075.409010759229</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>66399.31889208843</v>
@@ -21629,13 +21629,13 @@
         <v>11630</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>302767.3</v>
+        <v>302767.2999999999</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>340247</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>26.03330180567498</v>
+        <v>26.03330180567497</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>29.25597592433362</v>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>9527427.014243346</v>
+        <v>20244386.33014047</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>12769.54856496323</v>
@@ -21750,7 +21750,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>2070378.719270181</v>
+        <v>4603799.906081279</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>6308.862399938065</v>
@@ -21827,10 +21827,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1512528.863747452</v>
+        <v>3192642.648417211</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1132.428711516631</v>
+        <v>1132.428711516632</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -21860,13 +21860,13 @@
         <v>13991</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>419837.6900000001</v>
+        <v>419837.6899999999</v>
       </c>
       <c r="F28" s="66" t="n">
         <v>534426</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>30.00769709098707</v>
+        <v>30.00769709098706</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>38.19784146951612</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1132833.01533331</v>
+        <v>2390749.872993517</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>116.8701552582418</v>
@@ -21943,7 +21943,7 @@
         <v>261463</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>81.18517123287674</v>
+        <v>81.18517123287673</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>47.12743330930065</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>979794.7170563969</v>
+        <v>2067775.271073902</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>221.7412949757252</v>
@@ -22014,13 +22014,13 @@
         <v>19539</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>870253.0200000003</v>
+        <v>870253.02</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>795889.0000000001</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>44.53928143712576</v>
+        <v>44.53928143712575</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.7333538052101</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>894760.8252523051</v>
+        <v>1882729.081315658</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>85.39610497473396</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>844977.6324258684</v>
+        <v>1874443.697417282</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>1512.154619267931</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>828266.6217095607</v>
+        <v>1748477.591343567</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1141.362330658724</v>
@@ -22231,7 +22231,7 @@
         <v>5145932</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>55.23706857566056</v>
+        <v>55.23706857566055</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.12068941272423</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>561880.4868595749</v>
+        <v>1179459.544081972</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>75.42976213804248</v>
@@ -22308,7 +22308,7 @@
         <v>19553344</v>
       </c>
       <c r="G34" s="52" t="n">
-        <v>104.2267537280878</v>
+        <v>104.2267537280877</v>
       </c>
       <c r="H34" s="53" t="n">
         <v>87.04069513812843</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>543126.8570720808</v>
+        <v>1146224.065673437</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>147.9440078990487</v>
@@ -22414,19 +22414,19 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ERLEADA</t>
+          <t>GEMTESA</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>ONCOLOGY</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>474731.1790507135</v>
+        <v>1038104.793220708</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>91.69892652075751</v>
+        <v>745.1977318077995</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -22456,13 +22456,13 @@
         <v>441470</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35602246.06500001</v>
+        <v>35602246.065</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25008150</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.64476876118424</v>
+        <v>80.64476876118422</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.64745056289215</v>
@@ -22491,19 +22491,19 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>GEMTESA</t>
+          <t>ERLEADA</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>ONCOLOGY</t>
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>467965.6858161185</v>
+        <v>1001880.67496216</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>745.1977318077995</v>
+        <v>91.69892652075751</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -22568,19 +22568,19 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>COSENTYX UNOREADY</t>
+          <t>CREON</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>IMMUNOMODULATORS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>255919.8191131417</v>
+        <v>556092.3876004141</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>49.49809757259167</v>
+        <v>218.3281904331627</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -22616,7 +22616,7 @@
         <v>25048402</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.72709704800637</v>
+        <v>80.72709704800634</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.62204128134473</v>
@@ -22645,19 +22645,19 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>CREON</t>
+          <t>COSENTYX UNOREADY</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>IMMUNOMODULATORS</t>
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>250680.0442883839</v>
+        <v>540097.4960649851</v>
       </c>
       <c r="AI38" s="56" t="n">
-        <v>218.3281904331627</v>
+        <v>49.49809757259167</v>
       </c>
       <c r="AK38" s="123" t="n">
         <v>14</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>195500.5188064071</v>
+        <v>412587.5872085745</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>42.44315623196584</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>182290.017347786</v>
+        <v>405349.3966751762</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>135.8583557513883</v>
@@ -22823,7 +22823,7 @@
         <v>5486179</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>53.72736373577039</v>
+        <v>53.72736373577037</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.38616088295825</v>
@@ -22852,19 +22852,19 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>TYMLOS</t>
+          <t>STIOLTO RESPIMAT</t>
         </is>
       </c>
       <c r="AG41" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>171733.5542756848</v>
+        <v>379322.5203699532</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>87.07681527969977</v>
+        <v>431.8706227492556</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -22900,7 +22900,7 @@
         <v>19741600</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>103.6807104558114</v>
+        <v>103.6807104558113</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>86.9919272393979</v>
@@ -22929,19 +22929,19 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>STIOLTO RESPIMAT</t>
+          <t>TYMLOS</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>OSTEOPOROSIS AGENTS</t>
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>170994.2238487325</v>
+        <v>360773.9528913022</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>431.8706227492556</v>
+        <v>87.07681527969977</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23006,19 +23006,19 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>EMGALITY</t>
+          <t>SPIRIVA RESPIMAT</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>LAMA/ACH</t>
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>158542.5751055499</v>
+        <v>337882.0644103371</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>278.4775381563741</v>
+        <v>386.0779912577576</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -23054,7 +23054,7 @@
         <v>25542576</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>79.08928262793083</v>
+        <v>79.08928262793081</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>56.08070943505591</v>
@@ -23083,19 +23083,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>SPIRIVA RESPIMAT</t>
+          <t>EMGALITY</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>LAMA/ACH</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>152313.343536535</v>
+        <v>335330.9694267006</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>386.0779912577576</v>
+        <v>278.4775381563741</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -23167,13 +23167,13 @@
         <v>461917.9999999999</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>36582225.48500001</v>
+        <v>36582225.485</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>25844291</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>79.19636274187197</v>
+        <v>79.19636274187194</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>55.94995432089678</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>10355693.63595291</v>
+        <v>21992863.92148403</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>13910.91089562195</v>
@@ -23282,7 +23282,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>4289835.630702734</v>
+        <v>9047752.125374744</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>833.1049617729254</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2175280.559098161</v>
+        <v>4837064.997077794</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>7118.529077012619</v>
@@ -23449,7 +23449,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1520733.632185365</v>
+        <v>3209874.719263073</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1177.84129387238</v>
@@ -23507,10 +23507,10 @@
         <v>3190.244751579447</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>1582.361608270012</v>
+        <v>1582.361608270013</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1576.830955050484</v>
+        <v>1576.830955050485</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>18.90392960196367</v>
@@ -23519,7 +23519,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>3178.09649292246</v>
+        <v>3178.096492922461</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1190708.955268747</v>
+        <v>2505190.43109784</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>735.0779909466083</v>
@@ -23558,28 +23558,28 @@
         <v>3982</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>3542.055182527252</v>
+        <v>3542.055182527251</v>
       </c>
       <c r="K54" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>5098.787055046999</v>
+        <v>5098.787055046998</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>3687.309245058492</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -23594,7 +23594,7 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>1067263.534012992</v>
+        <v>2367548.356363691</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2208.314562841386</v>
@@ -23666,7 +23666,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>11128.94415726921</v>
@@ -23688,14 +23688,14 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>474141.7624759605</v>
+        <v>1038104.793220707</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>748.9058337482896</v>
+        <v>745.2309008463072</v>
       </c>
     </row>
     <row r="56">
@@ -23769,14 +23769,14 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>URINARY ANTISPASMODICS &amp; OAB DRUGS</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>1014336.049810069</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>745.2309008463072</v>
+        <v>748.9058337482898</v>
       </c>
     </row>
     <row r="57">
@@ -23801,13 +23801,13 @@
         <v>4506</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>1993.796490046238</v>
+        <v>1993.796490046237</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1170.184652629847</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>15.11113882740952</v>
+        <v>15.11113882740953</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>61.09093980085366</v>
@@ -23816,7 +23816,7 @@
         <v>3240.183221304347</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>1868.70084065676</v>
+        <v>1868.700840656761</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1085.072807591809</v>
@@ -23825,10 +23825,10 @@
         <v>12.50626329688559</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>60.91742114734843</v>
+        <v>60.91742114734842</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>3027.197332692803</v>
+        <v>3027.197332692804</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1591.150856265248</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>398761.8755321832</v>
+        <v>884587.5389810054</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>271.0766264439127</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>300514.915759722</v>
+        <v>631015.1404629167</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>476.1326761559805</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>223376.9656512656</v>
+        <v>489122.4209857815</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>372.2776007625407</v>
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>182290.017347786</v>
+        <v>405349.3966751762</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>135.8583557513883</v>
@@ -24178,7 +24178,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>180621.774075997</v>
+        <v>395736.6656563625</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>415.6220184636005</v>
@@ -24259,7 +24259,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>177023.5109933398</v>
+        <v>373554.7786346595</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>1554.212666503536</v>
@@ -24296,25 +24296,25 @@
         <v>35.33749470904132</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>4438.794081799459</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>2084.050763884925</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>36.15759299573634</v>
+        <v>36.15759299573628</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>427.0257108888128</v>
+        <v>427.0257108888129</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>4588.731260960696</v>
+        <v>4588.731260960689</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2089.05312889332</v>
@@ -24323,13 +24323,13 @@
         <v>2139.669162986289</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>37.02035917201493</v>
+        <v>37.02035917201496</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>4743.404806421916</v>
+        <v>4743.404806421915</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>151874.4287357912</v>
+        <v>336908.4042205453</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>508.2383233292842</v>
@@ -24421,7 +24421,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>144422.7022085875</v>
+        <v>321145.6999028071</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>33.16026275921071</v>
@@ -24469,7 +24469,7 @@
         <v>36614.95080324461</v>
       </c>
       <c r="P65" s="133" t="n">
-        <v>17969.80795994496</v>
+        <v>17969.80795994497</v>
       </c>
       <c r="Q65" s="134" t="n">
         <v>9277.056971434564</v>
@@ -24478,10 +24478,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S65" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>27906.60196401714</v>
+        <v>27906.60196401715</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>15805.42420356766</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>139384.4200027852</v>
+        <v>305444.85896696</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>203.221019681251</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>116144.0442576437</v>
+        <v>256058.0118291416</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>288.1655270376649</v>
@@ -24670,7 +24670,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>59901.00586583805</v>
+        <v>132880.5149454964</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>189.5942378418617</v>
@@ -24707,7 +24707,7 @@
         <v>289.1746794647207</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>996.7440921888074</v>
+        <v>996.7440921888075</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>63795.46038650115</v>
@@ -24751,7 +24751,7 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>46059.89161385121</v>
+        <v>102174.8908137713</v>
       </c>
       <c r="AH68" s="84" t="n">
         <v>55.49302736831311</v>
@@ -24908,7 +24908,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>9.13465504001347</v>
+        <v>9.134655040013469</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>5.086047772684145</v>
@@ -24920,7 +24920,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>14.22070281269762</v>
+        <v>14.22070281269761</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>9.637479088489158</v>
@@ -24941,7 +24941,7 @@
         <v>10.21236598571077</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>4.502300675384264</v>
+        <v>4.502300675384263</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -24975,7 +24975,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>0</v>
@@ -24987,7 +24987,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="P72" s="130" t="n">
         <v>0.9053496785836537</v>
@@ -25176,7 +25176,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8475.980194421152</v>
+        <v>8475.980194421149</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2873.388189285528</v>
@@ -25188,7 +25188,7 @@
         <v>21.5477444020895</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>11448.18834161465</v>
+        <v>11448.18834161464</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>9595.485484687017</v>
@@ -25206,7 +25206,7 @@
         <v>13104.65405550815</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>11757.0132811728</v>
+        <v>11757.01328117279</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3999.28898659296</v>
@@ -25578,7 +25578,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>4.547473508864641e-13</v>
@@ -25590,13 +25590,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -25620,7 +25620,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.092726157978177e-12</v>
       </c>
     </row>
     <row r="82">
@@ -25717,7 +25717,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="133" t="n">
-        <v>39.06922934125345</v>
+        <v>39.06922934125344</v>
       </c>
       <c r="K83" s="134" t="n">
         <v>1.904687071596461</v>
@@ -25729,10 +25729,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="135" t="n">
-        <v>40.97391641284991</v>
+        <v>40.9739164128499</v>
       </c>
       <c r="P83" s="133" t="n">
-        <v>46.73956313840376</v>
+        <v>46.73956313840377</v>
       </c>
       <c r="Q83" s="134" t="n">
         <v>2.252055773796713</v>
@@ -25744,7 +25744,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="135" t="n">
-        <v>48.99161891220047</v>
+        <v>48.99161891220048</v>
       </c>
       <c r="V83" s="133" t="n">
         <v>55.9718148645036</v>
@@ -25932,7 +25932,7 @@
         <v>11529.82467663058</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>9677.960572529688</v>
+        <v>9677.96057252969</v>
       </c>
       <c r="Q86" s="143" t="n">
         <v>3401.224593286631</v>
@@ -26155,7 +26155,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>3192.811159583555</v>
+        <v>3192.811159583556</v>
       </c>
     </row>
     <row r="90">
@@ -26180,28 +26180,28 @@
         <v>3983</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>3543.039089320718</v>
+        <v>3543.039089320716</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>5099.770961840464</v>
+        <v>5099.770961840463</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>3688.214594737075</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -26216,13 +26216,13 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>5522.659551408971</v>
+        <v>5522.65955140897</v>
       </c>
     </row>
     <row r="91">
@@ -26274,7 +26274,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>11128.94415726921</v>
@@ -26399,7 +26399,7 @@
         <v>11464.18632534378</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>4479.265978155642</v>
+        <v>4479.265978155641</v>
       </c>
       <c r="R93" s="131" t="n">
         <v>104.6184252717065</v>
@@ -26408,10 +26408,10 @@
         <v>83.78065942982869</v>
       </c>
       <c r="T93" s="132" t="n">
-        <v>16131.85138820096</v>
+        <v>16131.85138820095</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>13348.16413743805</v>
+        <v>13348.16413743804</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>5019.402142181207</v>
@@ -26423,7 +26423,7 @@
         <v>85.27829498014675</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>18577.58299574259</v>
+        <v>18577.58299574258</v>
       </c>
     </row>
     <row r="94">
@@ -26783,7 +26783,7 @@
         <v>3191</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1996.206591488692</v>
+        <v>1996.206591488699</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>2030.397059103354</v>
@@ -26792,25 +26792,25 @@
         <v>35.33749470904138</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>4438.794081799455</v>
+        <v>4438.794081799462</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>2084.050763884923</v>
+        <v>2084.050763884927</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>36.15759299573637</v>
+        <v>36.15759299573631</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>427.0257108888129</v>
+        <v>427.025710888813</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>4588.731260960694</v>
+        <v>4588.731260960691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2089.05312889332</v>
@@ -26822,10 +26822,10 @@
         <v>37.02035917201493</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>4743.404806421918</v>
+        <v>4743.404806421917</v>
       </c>
     </row>
     <row r="100">
@@ -26946,10 +26946,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S101" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>27955.59358292934</v>
+        <v>27955.59358292935</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>15861.39601843217</v>
@@ -27161,7 +27161,7 @@
         <v>307.7863336322335</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>1075.40901075923</v>
+        <v>1075.409010759229</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>66399.31889208843</v>
@@ -28153,13 +28153,13 @@
         <v>11630</v>
       </c>
       <c r="E25" s="40" t="n">
-        <v>302767.3</v>
+        <v>302767.2999999999</v>
       </c>
       <c r="F25" s="40" t="n">
         <v>340247</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>26.03330180567498</v>
+        <v>26.03330180567497</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>29.25597592433362</v>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>11834823.69873812</v>
+        <v>25373262.72142735</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>15323.44213046236</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>2553248.268577341</v>
+        <v>5721150.447202862</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>7444.457631926916</v>
@@ -28351,10 +28351,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>1908437.394728839</v>
+        <v>4065576.494787755</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>1356.632055243351</v>
+        <v>1356.63205524335</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -28384,13 +28384,13 @@
         <v>13991</v>
       </c>
       <c r="E28" s="66" t="n">
-        <v>419837.6900000001</v>
+        <v>419837.6899999999</v>
       </c>
       <c r="F28" s="66" t="n">
         <v>534426</v>
       </c>
       <c r="G28" s="67" t="n">
-        <v>30.00769709098707</v>
+        <v>30.00769709098706</v>
       </c>
       <c r="H28" s="68" t="n">
         <v>38.19784146951612</v>
@@ -28428,7 +28428,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>1394777.480434734</v>
+        <v>2970557.612117062</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>135.8083034709989</v>
@@ -28467,7 +28467,7 @@
         <v>261463</v>
       </c>
       <c r="G29" s="62" t="n">
-        <v>81.18517123287674</v>
+        <v>81.18517123287673</v>
       </c>
       <c r="H29" s="63" t="n">
         <v>47.12743330930065</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>1161490.728535689</v>
+        <v>2462895.913295984</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>101.1115501732342</v>
@@ -28538,13 +28538,13 @@
         <v>19539</v>
       </c>
       <c r="E30" s="71" t="n">
-        <v>870253.0200000003</v>
+        <v>870253.02</v>
       </c>
       <c r="F30" s="71" t="n">
         <v>795889.0000000001</v>
       </c>
       <c r="G30" s="72" t="n">
-        <v>44.53928143712576</v>
+        <v>44.53928143712575</v>
       </c>
       <c r="H30" s="73" t="n">
         <v>40.7333538052101</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>1025305.311138412</v>
+        <v>2183666.240293</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>226.6934806165784</v>
@@ -28636,19 +28636,19 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>TRULICITY</t>
+          <t>BREZTRI AEROSPHERE</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
+          <t>LABA LAMA COMBO</t>
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>951956.7819181825</v>
+        <v>2073398.899817029</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>1266.912187031183</v>
+        <v>1581.834704123797</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -28707,19 +28707,19 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>BREZTRI AEROSPHERE</t>
+          <t>TRULICITY</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>LABA LAMA COMBO</t>
+          <t>GLUCAGON-LIKE PEPTIDE-1 AGONISTS (GLP1)</t>
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>927715.9499239337</v>
+        <v>2028262.5211552</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>1581.834704123797</v>
+        <v>1266.912187031183</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -28755,7 +28755,7 @@
         <v>5145932</v>
       </c>
       <c r="G33" s="41" t="n">
-        <v>55.23706857566056</v>
+        <v>55.23706857566055</v>
       </c>
       <c r="H33" s="42" t="n">
         <v>24.12068941272423</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>688331.5046277494</v>
+        <v>1465988.961977387</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>174.6758114799117</v>
@@ -28832,7 +28832,7 @@
         <v>19553344</v>
       </c>
       <c r="G34" s="52" t="n">
-        <v>104.2267537280878</v>
+        <v>104.2267537280877</v>
       </c>
       <c r="H34" s="53" t="n">
         <v>87.04069513812843</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>628730.164857808</v>
+        <v>1329545.88104552</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>79.44564267427184</v>
@@ -28947,7 +28947,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>530215.6740375673</v>
+        <v>1129238.339928714</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>96.58097736872264</v>
@@ -28980,13 +28980,13 @@
         <v>441470</v>
       </c>
       <c r="E36" s="66" t="n">
-        <v>35602246.06500001</v>
+        <v>35602246.065</v>
       </c>
       <c r="F36" s="66" t="n">
         <v>25008150</v>
       </c>
       <c r="G36" s="67" t="n">
-        <v>80.64476876118424</v>
+        <v>80.64476876118422</v>
       </c>
       <c r="H36" s="68" t="n">
         <v>56.64745056289215</v>
@@ -29024,10 +29024,10 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>487821.5139308685</v>
+        <v>1090256.764879673</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>742.7981951113783</v>
+        <v>742.7981951113784</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>272901.3316407848</v>
+        <v>609920.871608384</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>224.4086305367263</v>
@@ -29140,7 +29140,7 @@
         <v>25048402</v>
       </c>
       <c r="G38" s="72" t="n">
-        <v>80.72709704800637</v>
+        <v>80.72709704800634</v>
       </c>
       <c r="H38" s="73" t="n">
         <v>56.62204128134473</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>272259.2763377744</v>
+        <v>579850.1030734864</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>50.48360469526197</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>217215.0101137436</v>
+        <v>486721.0790057078</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>151.6315108541245</v>
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>210373.2993539293</v>
+        <v>448047.1003784881</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>43.31664376719178</v>
@@ -29347,7 +29347,7 @@
         <v>5486179</v>
       </c>
       <c r="G41" s="41" t="n">
-        <v>53.72736373577039</v>
+        <v>53.72736373577037</v>
       </c>
       <c r="H41" s="42" t="n">
         <v>24.38616088295825</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>191057.7775751205</v>
+        <v>404434.7056109937</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>88.84273309357209</v>
@@ -29424,7 +29424,7 @@
         <v>19741600</v>
       </c>
       <c r="G42" s="52" t="n">
-        <v>103.6807104558114</v>
+        <v>103.6807104558113</v>
       </c>
       <c r="H42" s="53" t="n">
         <v>86.9919272393979</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>182586.9993398521</v>
+        <v>389572.3929354097</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>299.1015846322352</v>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>159886.4982688307</v>
+        <v>357338.3530092075</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>50.88335227286235</v>
@@ -29578,7 +29578,7 @@
         <v>25542576</v>
       </c>
       <c r="G44" s="67" t="n">
-        <v>79.08928262793083</v>
+        <v>79.08928262793081</v>
       </c>
       <c r="H44" s="68" t="n">
         <v>56.08070943505591</v>
@@ -29607,19 +29607,19 @@
       </c>
       <c r="AF44" s="82" t="inlineStr">
         <is>
-          <t>PROLIA</t>
+          <t>VUMERITY</t>
         </is>
       </c>
       <c r="AG44" s="82" t="inlineStr">
         <is>
-          <t>OSTEOPOROSIS AGENTS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>140848.0207766549</v>
+        <v>308785.7092207863</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>287.4323717733215</v>
+        <v>20.5575835795382</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -29691,13 +29691,13 @@
         <v>461917.9999999999</v>
       </c>
       <c r="E46" s="71" t="n">
-        <v>36582225.48500001</v>
+        <v>36582225.485</v>
       </c>
       <c r="F46" s="71" t="n">
         <v>25844291</v>
       </c>
       <c r="G46" s="72" t="n">
-        <v>79.19636274187197</v>
+        <v>79.19636274187194</v>
       </c>
       <c r="H46" s="73" t="n">
         <v>55.94995432089678</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>12786780.4806563</v>
+        <v>27401525.24258255</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>16590.35431749354</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>5063436.636972358</v>
+        <v>10773149.90217084</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>904.5383053961064</v>
@@ -29852,7 +29852,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>2686444.035724162</v>
+        <v>6019606.743895922</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>8399.864310874891</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>1917489.215001935</v>
+        <v>4084726.053270228</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>1402.764031737083</v>
@@ -30031,10 +30031,10 @@
         <v>3190.244751579447</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>1582.361608270012</v>
+        <v>1582.361608270013</v>
       </c>
       <c r="W53" s="128" t="n">
-        <v>1576.830955050484</v>
+        <v>1576.830955050485</v>
       </c>
       <c r="X53" s="128" t="n">
         <v>18.90392960196367</v>
@@ -30043,7 +30043,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="129" t="n">
-        <v>3178.09649292246</v>
+        <v>3178.096492922461</v>
       </c>
       <c r="AE53" s="121" t="n">
         <v>5</v>
@@ -30054,10 +30054,10 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>1333673.502638349</v>
+        <v>2828615.839624153</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>743.6685714703974</v>
+        <v>743.6685714703973</v>
       </c>
     </row>
     <row r="54">
@@ -30082,28 +30082,28 @@
         <v>3982</v>
       </c>
       <c r="J54" s="130" t="n">
-        <v>3542.055182527252</v>
+        <v>3542.055182527251</v>
       </c>
       <c r="K54" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L54" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M54" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="132" t="n">
-        <v>5098.787055046999</v>
+        <v>5098.787055046998</v>
       </c>
       <c r="P54" s="130" t="n">
         <v>3687.309245058492</v>
       </c>
       <c r="Q54" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R54" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S54" s="131" t="n">
         <v>0</v>
@@ -30118,7 +30118,7 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X54" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y54" s="131" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>935568.2296115442</v>
+        <v>2090948.35346896</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>1753.019134324906</v>
@@ -30190,7 +30190,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V55" s="130" t="n">
         <v>11128.94415726921</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>541497.4672068724</v>
+        <v>1167972.193335397</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>802.5309301690127</v>
@@ -30297,7 +30297,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>487821.5139308685</v>
+        <v>1090256.764879673</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>742.8312573455821</v>
@@ -30325,13 +30325,13 @@
         <v>4506</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>1993.796490046238</v>
+        <v>1993.796490046237</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1170.184652629847</v>
       </c>
       <c r="L57" s="131" t="n">
-        <v>15.11113882740952</v>
+        <v>15.11113882740953</v>
       </c>
       <c r="M57" s="131" t="n">
         <v>61.09093980085366</v>
@@ -30340,7 +30340,7 @@
         <v>3240.183221304347</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>1868.70084065676</v>
+        <v>1868.700840656761</v>
       </c>
       <c r="Q57" s="131" t="n">
         <v>1085.072807591809</v>
@@ -30349,10 +30349,10 @@
         <v>12.50626329688559</v>
       </c>
       <c r="S57" s="131" t="n">
-        <v>60.91742114734843</v>
+        <v>60.91742114734842</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>3027.197332692803</v>
+        <v>3027.197332692804</v>
       </c>
       <c r="V57" s="130" t="n">
         <v>1591.150856265248</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>432787.8299096154</v>
+        <v>967259.2246175914</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>278.7864509401118</v>
@@ -30459,10 +30459,10 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>331905.7983517753</v>
+        <v>702202.0438559363</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>485.7234868073287</v>
+        <v>485.7234868073288</v>
       </c>
     </row>
     <row r="59">
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>262546.1259968012</v>
+        <v>578521.4165315751</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>415.4990302110716</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>217215.0101137436</v>
+        <v>486721.0790057077</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>151.6315108541245</v>
@@ -30702,7 +30702,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>176539.9012613627</v>
+        <v>375938.1019680882</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>1481.646477104487</v>
@@ -30783,7 +30783,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>157693.407691526</v>
+        <v>352436.9048983332</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>504.2537348743826</v>
@@ -30820,25 +30820,25 @@
         <v>35.33749470904132</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N63" s="132" t="n">
         <v>4438.794081799459</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>2084.050763884925</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>36.15759299573634</v>
+        <v>36.15759299573628</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>427.0257108888128</v>
+        <v>427.0257108888129</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>4588.731260960696</v>
+        <v>4588.731260960689</v>
       </c>
       <c r="V63" s="130" t="n">
         <v>2089.05312889332</v>
@@ -30847,13 +30847,13 @@
         <v>2139.669162986289</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>37.02035917201493</v>
+        <v>37.02035917201496</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>4743.404806421916</v>
+        <v>4743.404806421915</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30864,10 +30864,10 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>144621.5312714436</v>
+        <v>324058.3959231692</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>31.21707136152096</v>
+        <v>31.21707136152097</v>
       </c>
     </row>
     <row r="64">
@@ -30945,7 +30945,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>123008.661480873</v>
+        <v>272960.5290254793</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>285.3184516305328</v>
@@ -30993,7 +30993,7 @@
         <v>36614.95080324461</v>
       </c>
       <c r="P65" s="133" t="n">
-        <v>17969.80795994496</v>
+        <v>17969.80795994497</v>
       </c>
       <c r="Q65" s="134" t="n">
         <v>9277.056971434564</v>
@@ -31002,10 +31002,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S65" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T65" s="135" t="n">
-        <v>27906.60196401714</v>
+        <v>27906.60196401715</v>
       </c>
       <c r="V65" s="133" t="n">
         <v>15805.42420356766</v>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>121074.3209833559</v>
+        <v>265333.3173157114</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>178.5021877230272</v>
@@ -31113,7 +31113,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>79987.19625374628</v>
+        <v>173992.285298893</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>194.5461142000632</v>
@@ -31194,7 +31194,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>57430.9172970456</v>
+        <v>128355.2371272054</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>167.7757329510203</v>
@@ -31231,7 +31231,7 @@
         <v>289.1746794647207</v>
       </c>
       <c r="M68" s="143" t="n">
-        <v>996.7440921888074</v>
+        <v>996.7440921888075</v>
       </c>
       <c r="N68" s="144" t="n">
         <v>63795.46038650115</v>
@@ -31275,10 +31275,10 @@
         </is>
       </c>
       <c r="AG68" s="125" t="n">
-        <v>48063.971086413</v>
+        <v>107520.5816121111</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>54.47251059500983</v>
+        <v>54.47251059500984</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -31432,7 +31432,7 @@
         <v>12</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>9.13465504001347</v>
+        <v>9.134655040013469</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>5.086047772684145</v>
@@ -31444,7 +31444,7 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>14.22070281269762</v>
+        <v>14.22070281269761</v>
       </c>
       <c r="P71" s="127" t="n">
         <v>9.637479088489158</v>
@@ -31465,7 +31465,7 @@
         <v>10.21236598571077</v>
       </c>
       <c r="W71" s="128" t="n">
-        <v>4.502300675384264</v>
+        <v>4.502300675384263</v>
       </c>
       <c r="X71" s="128" t="n">
         <v>0</v>
@@ -31499,7 +31499,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="130" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="K72" s="131" t="n">
         <v>0</v>
@@ -31511,7 +31511,7 @@
         <v>0</v>
       </c>
       <c r="N72" s="132" t="n">
-        <v>0.9839067934655528</v>
+        <v>0.9839067934655525</v>
       </c>
       <c r="P72" s="130" t="n">
         <v>0.9053496785836537</v>
@@ -31700,7 +31700,7 @@
         <v>2799</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>8475.980194421152</v>
+        <v>8475.980194421149</v>
       </c>
       <c r="K75" s="131" t="n">
         <v>2873.388189285528</v>
@@ -31712,7 +31712,7 @@
         <v>21.5477444020895</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>11448.18834161465</v>
+        <v>11448.18834161464</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>9595.485484687017</v>
@@ -31730,7 +31730,7 @@
         <v>13104.65405550815</v>
       </c>
       <c r="V75" s="130" t="n">
-        <v>11757.0132811728</v>
+        <v>11757.01328117279</v>
       </c>
       <c r="W75" s="131" t="n">
         <v>3999.28898659296</v>
@@ -32102,7 +32102,7 @@
         <v>0</v>
       </c>
       <c r="J81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="K81" s="131" t="n">
         <v>4.547473508864641e-13</v>
@@ -32114,13 +32114,13 @@
         <v>0</v>
       </c>
       <c r="N81" s="132" t="n">
-        <v>-3.183231456205249e-12</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="P81" s="130" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.818989403545856e-12</v>
       </c>
       <c r="Q81" s="131" t="n">
-        <v>0</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="R81" s="131" t="n">
         <v>0</v>
@@ -32129,13 +32129,13 @@
         <v>0</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>-3.637978807091713e-12</v>
+        <v>-1.364242052659392e-12</v>
       </c>
       <c r="V81" s="130" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="W81" s="131" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="X81" s="131" t="n">
         <v>0</v>
@@ -32144,7 +32144,7 @@
         <v>0</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>4.092726157978177e-12</v>
       </c>
     </row>
     <row r="82">
@@ -32241,7 +32241,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="133" t="n">
-        <v>39.06922934125345</v>
+        <v>39.06922934125344</v>
       </c>
       <c r="K83" s="134" t="n">
         <v>1.904687071596461</v>
@@ -32253,10 +32253,10 @@
         <v>0</v>
       </c>
       <c r="N83" s="135" t="n">
-        <v>40.97391641284991</v>
+        <v>40.9739164128499</v>
       </c>
       <c r="P83" s="133" t="n">
-        <v>46.73956313840376</v>
+        <v>46.73956313840377</v>
       </c>
       <c r="Q83" s="134" t="n">
         <v>2.252055773796713</v>
@@ -32268,7 +32268,7 @@
         <v>0</v>
       </c>
       <c r="T83" s="135" t="n">
-        <v>48.99161891220047</v>
+        <v>48.99161891220048</v>
       </c>
       <c r="V83" s="133" t="n">
         <v>55.9718148645036</v>
@@ -32456,7 +32456,7 @@
         <v>11529.82467663058</v>
       </c>
       <c r="P86" s="142" t="n">
-        <v>9677.960572529688</v>
+        <v>9677.96057252969</v>
       </c>
       <c r="Q86" s="143" t="n">
         <v>3401.224593286631</v>
@@ -32679,7 +32679,7 @@
         <v>0</v>
       </c>
       <c r="Z89" s="129" t="n">
-        <v>3192.811159583555</v>
+        <v>3192.811159583556</v>
       </c>
     </row>
     <row r="90">
@@ -32704,28 +32704,28 @@
         <v>3983</v>
       </c>
       <c r="J90" s="130" t="n">
-        <v>3543.039089320718</v>
+        <v>3543.039089320716</v>
       </c>
       <c r="K90" s="131" t="n">
         <v>1526.46400626283</v>
       </c>
       <c r="L90" s="131" t="n">
-        <v>30.2678662569167</v>
+        <v>30.26786625691671</v>
       </c>
       <c r="M90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N90" s="132" t="n">
-        <v>5099.770961840464</v>
+        <v>5099.770961840463</v>
       </c>
       <c r="P90" s="130" t="n">
         <v>3688.214594737075</v>
       </c>
       <c r="Q90" s="131" t="n">
-        <v>1576.251542953442</v>
+        <v>1576.251542953443</v>
       </c>
       <c r="R90" s="131" t="n">
-        <v>31.07119871716295</v>
+        <v>31.07119871716296</v>
       </c>
       <c r="S90" s="131" t="n">
         <v>0</v>
@@ -32740,13 +32740,13 @@
         <v>1631.605949188496</v>
       </c>
       <c r="X90" s="131" t="n">
-        <v>31.90956796619944</v>
+        <v>31.90956796619945</v>
       </c>
       <c r="Y90" s="131" t="n">
         <v>0</v>
       </c>
       <c r="Z90" s="132" t="n">
-        <v>5522.659551408971</v>
+        <v>5522.65955140897</v>
       </c>
     </row>
     <row r="91">
@@ -32798,7 +32798,7 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>11173.5301623466</v>
+        <v>11173.53016234659</v>
       </c>
       <c r="V91" s="130" t="n">
         <v>11128.94415726921</v>
@@ -32923,7 +32923,7 @@
         <v>11464.18632534378</v>
       </c>
       <c r="Q93" s="131" t="n">
-        <v>4479.265978155642</v>
+        <v>4479.265978155641</v>
       </c>
       <c r="R93" s="131" t="n">
         <v>104.6184252717065</v>
@@ -32932,10 +32932,10 @@
         <v>83.78065942982869</v>
       </c>
       <c r="T93" s="132" t="n">
-        <v>16131.85138820096</v>
+        <v>16131.85138820095</v>
       </c>
       <c r="V93" s="130" t="n">
-        <v>13348.16413743805</v>
+        <v>13348.16413743804</v>
       </c>
       <c r="W93" s="131" t="n">
         <v>5019.402142181207</v>
@@ -32947,7 +32947,7 @@
         <v>85.27829498014675</v>
       </c>
       <c r="Z93" s="132" t="n">
-        <v>18577.58299574259</v>
+        <v>18577.58299574258</v>
       </c>
     </row>
     <row r="94">
@@ -33307,7 +33307,7 @@
         <v>3191</v>
       </c>
       <c r="J99" s="130" t="n">
-        <v>1996.206591488692</v>
+        <v>1996.206591488699</v>
       </c>
       <c r="K99" s="131" t="n">
         <v>2030.397059103354</v>
@@ -33316,25 +33316,25 @@
         <v>35.33749470904138</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>376.8529364983675</v>
+        <v>376.8529364983676</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>4438.794081799455</v>
+        <v>4438.794081799462</v>
       </c>
       <c r="P99" s="130" t="n">
-        <v>2041.497193191222</v>
+        <v>2041.497193191215</v>
       </c>
       <c r="Q99" s="131" t="n">
-        <v>2084.050763884923</v>
+        <v>2084.050763884927</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>36.15759299573637</v>
+        <v>36.15759299573631</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>427.0257108888129</v>
+        <v>427.025710888813</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>4588.731260960694</v>
+        <v>4588.731260960691</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2089.05312889332</v>
@@ -33346,10 +33346,10 @@
         <v>37.02035917201493</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>477.6621553702923</v>
+        <v>477.6621553702921</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>4743.404806421918</v>
+        <v>4743.404806421917</v>
       </c>
     </row>
     <row r="100">
@@ -33470,10 +33470,10 @@
         <v>124.6682213736844</v>
       </c>
       <c r="S101" s="134" t="n">
-        <v>535.0688112639338</v>
+        <v>535.0688112639336</v>
       </c>
       <c r="T101" s="135" t="n">
-        <v>27955.59358292934</v>
+        <v>27955.59358292935</v>
       </c>
       <c r="V101" s="133" t="n">
         <v>15861.39601843217</v>
@@ -33685,7 +33685,7 @@
         <v>307.7863336322335</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>1075.40901075923</v>
+        <v>1075.409010759229</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>66399.31889208843</v>
